--- a/sample-salary-data.xlsx
+++ b/sample-salary-data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Details" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t xml:space="preserve">Employee ID</t>
   </si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">bfms92@gmail.com</t>
+    <t xml:space="preserve">yogeshmamgain2611@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9876543210</t>
@@ -111,9 +111,6 @@
     <t xml:space="preserve">Product</t>
   </si>
   <si>
-    <t xml:space="preserve">anubhaventerprises23@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">9876543211</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t xml:space="preserve">Junior Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">badolaarpit20@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">9876543212</t>
@@ -272,12 +266,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -473,186 +471,191 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>44576.0001157407</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="M3" s="2" t="n">
+        <v>44367.0001157407</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>44367.0001157407</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>44995.0001157407</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="yogeshmamgain2611@gmail.com"/>
+    <hyperlink ref="E3" r:id="rId2" display="yogeshmamgain2611@gmail.com"/>
+    <hyperlink ref="E4" r:id="rId3" display="yogeshmamgain2611@gmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -671,71 +674,71 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>19500</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>10500</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -758,117 +761,117 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>7800</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>975</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>4200</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>525</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>100</v>
       </c>
     </row>
